--- a/momentum_sharpe_jun2023_announcement.xlsx
+++ b/momentum_sharpe_jun2023_announcement.xlsx
@@ -573,7 +573,7 @@
         <v>1.259</v>
       </c>
       <c r="D8" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>-0.358</v>
       </c>
       <c r="D11" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="12">
